--- a/input/old/Metadata _SKN_S_SW_10_06_MD_CHNG_LOG.xlsx
+++ b/input/old/Metadata _SKN_S_SW_10_06_MD_CHNG_LOG.xlsx
@@ -413,51 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A8:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -466,11 +424,9 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SW_10_06_CUST_CHNG</t>
+          <t>SW_10_01_CREDIT_APP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -480,23 +436,9 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Customers Master General Change Log</t>
+          <t>Credit Management Approvals</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
